--- a/doc/交付/2026-10-03-答辩与商业计划书/Blocky-Studio-财务测算-2026-10-03.xlsx
+++ b/doc/交付/2026-10-03-答辩与商业计划书/Blocky-Studio-财务测算-2026-10-03.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Folder\Blocky-AI\doc\交付\2026-10-03-答辩与商业计划书\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907EDC5C-800C-42F2-9600-168AB58A7934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1218,58 +1213,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{9CFD22A2-4727-4C1B-83BD-92CDC501259E}">
-  <we:reference id="wa200003696" version="1.3.0.0" store="zh-CN" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200003696" version="1.3.0.0" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{B867B85C-A15D-4AD4-A744-2F3DEBB46254}">
-  <we:reference id="wa200005271" version="2.5.4.0" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200005271" version="2.5.4.0" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension3.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{BB3572F9-0D3C-48B0-8F12-2D06E87A2520}">
-  <we:reference id="wa200005502" version="1.0.0.11" store="zh-CN" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200005502" version="1.0.0.11" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="docId" value="&quot;-oZB-_HnEl8NCWtLw0TUo&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:L23"/>
